--- a/data/outputs/Data_Figure_2.xlsx
+++ b/data/outputs/Data_Figure_2.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\01_3rd_submission\Manuscript_datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\02_Final_revision\0_Final_submission\Manuscript_datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7BF28D-994E-403D-BD73-F5A67046702C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5210715E-95CE-4865-ABD4-D04B743819E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="2175" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fig 2" sheetId="10" r:id="rId1"/>
+    <sheet name="Figure 2" sheetId="10" r:id="rId1"/>
     <sheet name="Baseline" sheetId="9" r:id="rId2"/>
     <sheet name="Roadmap-70" sheetId="1" r:id="rId3"/>
     <sheet name="Roadmap-30-Bio" sheetId="2" r:id="rId4"/>
